--- a/ZFDelphi PowerQuery/DATA DELPHI/Questionare DELPHI - 01.xlsx
+++ b/ZFDelphi PowerQuery/DATA DELPHI/Questionare DELPHI - 01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Research\VBAFuzzy\ZFDelphi PowerQuery\DATA DELPHI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0404FCA2-2ADF-4FFF-91DA-07AC23FA9BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092E2720-6E01-4215-8789-1475F821C6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -515,15 +515,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -535,6 +526,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1361,53 +1361,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
       <c r="U1" s="9"/>
       <c r="V1" s="9"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1454,36 +1454,36 @@
       <c r="E9" s="10"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
     </row>
     <row r="13" spans="1:22" ht="98.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -1510,11 +1510,11 @@
         <v>83</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="6" t="str">
         <f>_xlfn.IFNA(_xlfn.CONCAT(INDEX('REF SHEET'!$F$2:$F$6,MATCH(B16,'REF SHEET'!$H$2:$H$6,0)),";",INDEX('REF SHEET'!$G$2:$G$6,MATCH(C16,'REF SHEET'!$I$2:$I$6,0))),"")</f>
-        <v>VI;VH</v>
+        <v>VI;H</v>
       </c>
       <c r="E16" s="5"/>
     </row>
@@ -1526,11 +1526,11 @@
         <v>83</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D17" s="6" t="str">
         <f>_xlfn.IFNA(_xlfn.CONCAT(INDEX('REF SHEET'!$F$2:$F$6,MATCH(B17,'REF SHEET'!$H$2:$H$6,0)),";",INDEX('REF SHEET'!$G$2:$G$6,MATCH(C17,'REF SHEET'!$I$2:$I$6,0))),"")</f>
-        <v>VI;VH</v>
+        <v>VI;H</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -1542,11 +1542,11 @@
         <v>83</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D18" s="6" t="str">
         <f>_xlfn.IFNA(_xlfn.CONCAT(INDEX('REF SHEET'!$F$2:$F$6,MATCH(B18,'REF SHEET'!$H$2:$H$6,0)),";",INDEX('REF SHEET'!$G$2:$G$6,MATCH(C18,'REF SHEET'!$I$2:$I$6,0))),"")</f>
-        <v>VI;VH</v>
+        <v>VI;H</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -1558,11 +1558,11 @@
         <v>83</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D19" s="6" t="str">
         <f>_xlfn.IFNA(_xlfn.CONCAT(INDEX('REF SHEET'!$F$2:$F$6,MATCH(B19,'REF SHEET'!$H$2:$H$6,0)),";",INDEX('REF SHEET'!$G$2:$G$6,MATCH(C19,'REF SHEET'!$I$2:$I$6,0))),"")</f>
-        <v>VI;VH</v>
+        <v>VI;H</v>
       </c>
       <c r="E19" s="5"/>
     </row>
@@ -1574,16 +1574,21 @@
         <v>83</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D20" s="6" t="str">
         <f>_xlfn.IFNA(_xlfn.CONCAT(INDEX('REF SHEET'!$F$2:$F$6,MATCH(B20,'REF SHEET'!$H$2:$H$6,0)),";",INDEX('REF SHEET'!$G$2:$G$6,MATCH(C20,'REF SHEET'!$I$2:$I$6,0))),"")</f>
-        <v>VI;VH</v>
+        <v>VI;H</v>
       </c>
       <c r="E20" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:T1"/>
@@ -1591,11 +1596,6 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Example:" prompt="Nguyễn Văn A_x000a_" sqref="B6:E6" xr:uid="{D185ADD3-C280-4E1F-89F5-7495A756D9DA}"/>
